--- a/ai_logs/Nghia_AI_Log.xlsx
+++ b/ai_logs/Nghia_AI_Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daomi\.gemini\antigravity\scratch\Food_delivery-main\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84186D47-C64D-43AC-AB58-8B03528854E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2DE6936-8BC4-4E86-8EC6-1B5510578AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="285">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -725,6 +725,201 @@
   </si>
   <si>
     <t>Code phương thức tearDown() trong JUnit test chứa cả hai dòng lệnh này và kết quả test chạy liên tục không còn bị lỗi khóa tệp.</t>
+  </si>
+  <si>
+    <t>DataAnalyzer</t>
+  </si>
+  <si>
+    <t>Cần đọc file log CSV để phát hiện lỗi gán 1 đơn cho nhiều tài xế do Race Condition.</t>
+  </si>
+  <si>
+    <t>"Viết hàm detectDoubleAssignments đọc file assignments_log.csv, đếm số đơn hàng bị gán cho 2 tài xế khác nhau trở lên."</t>
+  </si>
+  <si>
+    <t>AI viết ra hàm dùng Map&lt;Integer, Set&lt;Integer&gt;&gt; để lưu danh sách ID tài xế theo mã đơn hàng và đếm các Set có size &gt;= 2.</t>
+  </si>
+  <si>
+    <t>Giữ nguyên. Code AI viết rất tốt, xử lý được việc trùng lặp bằng HashSet. Chỉ bổ sung thêm comment tiếng Việt cho dễ hiểu.</t>
+  </si>
+  <si>
+    <t>Cần phát hiện lỗi bán vượt mức tồn kho (Overselling) trong kho dữ liệu.</t>
+  </si>
+  <si>
+    <t>"Viết hàm detectOversellItems quét toàn bộ danh sách MenuItem, trả về số món ăn có số lượng tồn kho bị âm."</t>
+  </si>
+  <si>
+    <t>AI viết vòng lặp for duyệt qua menuItemRepo.readAll(), kiểm tra getStockQty() &lt; 0 và tăng biến đếm.</t>
+  </si>
+  <si>
+    <t>Giữ nguyên. Logic chuẩn xác và đơn giản, chạy đúng với yêu cầu.</t>
+  </si>
+  <si>
+    <t>Đếm số lượng tài xế bị gán từ 2 đơn hàng cùng lúc (Overload).</t>
+  </si>
+  <si>
+    <t>"Viết hàm detectDriverOverload đếm xem có bao nhiêu tài xế đang xử lý từ 2 đơn hàng (CONFIRMED hoặc DELIVERING) trở lên."</t>
+  </si>
+  <si>
+    <t>AI cung cấp đoạn code dùng vòng lặp duyệt qua danh sách tài xế, sau đó gọi hàm driver.getActiveOrders().size() &gt;= 2 để đếm.</t>
+  </si>
+  <si>
+    <t>Sửa đổi lớn. Class Driver không hề có hàm getActiveOrders(). Tự viết lại bằng cách duyệt List Order và dùng Map để đếm số đơn theo driverId. (Xem Bảng 2)</t>
+  </si>
+  <si>
+    <t>Integration</t>
+  </si>
+  <si>
+    <t>MainApplication</t>
+  </si>
+  <si>
+    <t>Cần hiển thị kết quả 3 hàm detect trên ra màn hình Console dưới dạng cột ERR:DA/OS/DL.</t>
+  </si>
+  <si>
+    <t>"Làm sao gọi 3 hàm detect này trong MainApplication và in ra định dạng ERR:DA/OS/DL ở cuối mỗi vòng lặp?"</t>
+  </si>
+  <si>
+    <t>AI hướng dẫn tạo object DataAnalyzer, gọi 3 hàm và dùng String.format("ERR:%d/%d/%d", da, os, dl).</t>
+  </si>
+  <si>
+    <t>Sửa đổi nhỏ. Điều chỉnh lại độ rộng cột (padding) trong String.format để in ra thẳng hàng với header của bảng Console.</t>
+  </si>
+  <si>
+    <t>Explanation</t>
+  </si>
+  <si>
+    <t>Cần giải thích lý do khác biệt kết quả giữa các chế độ chạy.</t>
+  </si>
+  <si>
+    <t>"Tại sao khi chạy NO_LOCK thì cột ERR báo lỗi 3/5/2, còn SYNCHRONIZED lại báo 0/0/0?"</t>
+  </si>
+  <si>
+    <t>AI giải thích rõ NO_LOCK cho phép các luồng ghi đè dữ liệu lên nhau gây lỗi. SYNCHRONIZED khóa luồng tuần tự nên dữ liệu an toàn 100%.</t>
+  </si>
+  <si>
+    <t>Reflection: Câu trả lời rất logic, được dùng để đưa vào file báo cáo đồ án giải thích cơ chế Thread-safe.</t>
+  </si>
+  <si>
+    <t>Code Optimization</t>
+  </si>
+  <si>
+    <t>Muốn tối ưu hàm detectDoubleAssignments bằng Java 8 Stream cho gọn.</t>
+  </si>
+  <si>
+    <t>"Có cách nào dùng Java 8 Stream để viết lại hàm detectDoubleAssignments cho ngắn và chạy nhanh hơn vòng lặp while không?"</t>
+  </si>
+  <si>
+    <t>AI đề xuất dùng: Files.lines(path).distinct().count() và khẳng định nó sẽ đếm được các đơn hàng gán đôi.</t>
+  </si>
+  <si>
+    <t>Bác bỏ hoàn toàn. Logic sai bét. Hàm distinct().count() chỉ đếm số dòng không trùng lặp, chứ không nhóm theo OrderID. (Xem Bảng 2)</t>
+  </si>
+  <si>
+    <t>OrderService</t>
+  </si>
+  <si>
+    <t>Đã bật chế độ OPTIMISTIC locking nhưng vẫn bị lỗi Oversell thi thoảng xuất hiện.</t>
+  </si>
+  <si>
+    <t>"Tại sao chạy chế độ OPTIMISTIC mà hàm detectOversellItems thỉnh thoảng vẫn trả về 1 món bị âm?"</t>
+  </si>
+  <si>
+    <t>AI phân tích rằng Optimistic Locking sẽ văng Exception nếu xung đột version, nhưng code hiện tại đang bỏ qua lỗi thay vì cho luồng đó Retry.</t>
+  </si>
+  <si>
+    <t>Sửa đổi lớn. Bổ sung vòng lặp while(retry &lt; 3) vào OrderService để luồng lấy lại version mới nhất và thử trừ kho lại.</t>
+  </si>
+  <si>
+    <t>Feature Addition</t>
+  </si>
+  <si>
+    <t>Muốn bộ quét lỗi này chạy ngầm liên tục thay vì chỉ chạy 1 lần ở cuối.</t>
+  </si>
+  <si>
+    <t>"Tôi muốn 3 hàm detect này tự động chạy ngầm (background thread) quét hệ thống mỗi 5 giây thì làm thế nào?"</t>
+  </si>
+  <si>
+    <t>Code Review</t>
+  </si>
+  <si>
+    <t>Lo ngại về hiệu năng của hàm overload khi data lớn.</t>
+  </si>
+  <si>
+    <t>"Đoạn code dùng Map&lt;Integer, Integer&gt; trong detectDriverOverload có gây tràn RAM nếu có 1 triệu đơn hàng không?"</t>
+  </si>
+  <si>
+    <t>AI tính toán kích thước object Integer và kết luận với 1 triệu đơn hàng, Map chỉ tốn khoảng vài chục MB RAM, không lo bị tràn.</t>
+  </si>
+  <si>
+    <t>AI khẳng định rằng CsvRepository có sẵn một trigger ngầm tự động ghi log mọi thay đổi của file vào assignments_log.csv.</t>
+  </si>
+  <si>
+    <t>AI cung cấp code khởi tạo ScheduledExecutorService và gọi scheduleAtFixedRate() để chạy quét định kỳ.</t>
+  </si>
+  <si>
+    <t>Sửa đổi nhỏ. Thêm lệnh executor.shutdown() vào cuối luồng chính để ngăn chương trình bị treo (memory leak) khi kết thúc test.</t>
+  </si>
+  <si>
+    <t>Reflection: Yên tâm giữ lại cấu trúc Map để chạy, kiểm thử với file 100.000 dòng vẫn mượt mà không bị OutOfMemory.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Repository	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không hiểu file assignments_log.csv từ đâu mà có để hàm detect đọc.	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"File assignments_log.csv được ghi dữ liệu vào lúc nào trong hệ thống?"	</t>
+  </si>
+  <si>
+    <t>Bác bỏ hoàn toàn. CSV không có khái niệm trigger như SQL. Phải tự tay viết hàm FileWriter(logFile, true) vào OrderService.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataAnalyzer	</t>
+  </si>
+  <si>
+    <t>AI tự tin cung cấp dòng code: if(driver.getActiveOrders().size() &gt;= 2) để kiểm tra số đơn hàng của tài xế.</t>
+  </si>
+  <si>
+    <t>Class Driver (Model) trong code hiện tại chỉ chứa các thuộc tính cơ bản như id, name, status, không hề chứa list orders hay hàm getActiveOrders().</t>
+  </si>
+  <si>
+    <t>Khi copy paste đoạn code của AI vào IDE (NetBeans/Eclipse), IDE lập tức báo gạch đỏ lỗi "Cannot resolve method".</t>
+  </si>
+  <si>
+    <t>Xóa bỏ code của AI. Tự viết vòng lặp quét danh sách Order, check điều kiện o.getDriverId() và đẩy vào HashMap để tự đếm thủ công. (Chính là đoạn code chuẩn bạn đang có).</t>
+  </si>
+  <si>
+    <t>AI khẳng định câu lệnh Files.lines(path).distinct().count() là cách dùng Stream tối ưu để phát hiện việc gán trùng tài xế.</t>
+  </si>
+  <si>
+    <t>Câu lệnh này chỉ có tác dụng đếm số lượng dòng văn bản không giống nhau hoàn toàn trong file CSV, không hề nhóm hay so sánh driverId theo orderId. Nếu 1 order có 2 dòng (gán cho 2 driver), nó tính là 2 dòng hợp lệ chứ không báo lỗi.</t>
+  </si>
+  <si>
+    <t>Khi chạy thử với file cố tình tạo lỗi double assign, hàm của AI trả về kết quả đếm tổng số dòng, hoàn toàn sai lệch với kết quả thực tế.</t>
+  </si>
+  <si>
+    <t>AI giải thích nguyên lý rằng file CSV được quản lý bởi CsvRepository và nó có cơ chế "Trigger tự động" (như SQL Server) để sinh ra file log.</t>
+  </si>
+  <si>
+    <t>File CSV chỉ là text file (Flat file), không có database engine nào đứng sau để thực thi các "trigger ngầm" hay lưu lịch sử thay đổi tự động.</t>
+  </si>
+  <si>
+    <t>Bằng kiến thức cơ bản về Database và File I/O, tôi nhận ra AI đang lấy râu ông nọ (Database SQL) cắm cằm bà kia (File CSV).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricated Method </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flawed Logic / Semantic Hallucination </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Factual Inaccuracy </t>
+  </si>
+  <si>
+    <t>Bỏ qua gợi ý tối ưu của AI. Quay về sử dụng đoạn code dùng vòng lặp while(readLine) và HashSet truyền thống vì logic chính xác hơn.</t>
+  </si>
+  <si>
+    <t>Bỏ qua lời giải thích của AI. Tự xác định lại rằng lịch sử gán tài xế phải được lưu thủ công bằng lệnh BufferedWriter mỗi khi Controller gọi hàm dispatch thành công.</t>
   </si>
 </sst>
 </file>
@@ -734,7 +929,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -826,6 +1021,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -891,7 +1099,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -931,9 +1139,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -948,9 +1153,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -959,6 +1161,25 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -979,7 +1200,7 @@
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -987,34 +1208,34 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -1272,14 +1493,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -1498,7 +1719,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1511,484 +1732,654 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="29" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="30">
         <v>1</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="7"/>
+      <c r="H4" s="30"/>
     </row>
     <row r="5" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
+      <c r="A5" s="30">
         <v>2</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="H5" s="7"/>
+      <c r="H5" s="30"/>
     </row>
     <row r="6" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7">
+      <c r="A6" s="30">
         <v>3</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="30" t="s">
         <v>137</v>
       </c>
-      <c r="H6" s="7"/>
+      <c r="H6" s="30"/>
     </row>
     <row r="7" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7">
+      <c r="A7" s="30">
         <v>4</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="30" t="s">
         <v>140</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="H7" s="7"/>
+      <c r="H7" s="30"/>
     </row>
     <row r="8" spans="1:8" ht="95.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7">
+      <c r="A8" s="30">
         <v>5</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="30" t="s">
         <v>143</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="30" t="s">
         <v>144</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="30" t="s">
         <v>145</v>
       </c>
-      <c r="H8" s="7"/>
+      <c r="H8" s="30"/>
     </row>
     <row r="9" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7">
+      <c r="A9" s="30">
         <v>6</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="H9" s="7"/>
+      <c r="H9" s="30"/>
     </row>
     <row r="10" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7">
+      <c r="A10" s="30">
         <v>7</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="30" t="s">
         <v>215</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="30" t="s">
         <v>173</v>
       </c>
-      <c r="H10" s="7"/>
+      <c r="H10" s="30"/>
     </row>
     <row r="11" spans="1:8" ht="112.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7">
+      <c r="A11" s="30">
         <v>8</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="30" t="s">
         <v>148</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="30" t="s">
         <v>150</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="30" t="s">
         <v>151</v>
       </c>
-      <c r="H11" s="7"/>
+      <c r="H11" s="30"/>
     </row>
     <row r="12" spans="1:8" ht="119.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7">
+      <c r="A12" s="30">
         <v>9</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="H12" s="7"/>
+      <c r="H12" s="30"/>
     </row>
     <row r="13" spans="1:8" ht="112.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7">
+      <c r="A13" s="30">
         <v>10</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="31" t="s">
         <v>166</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="H13" s="7"/>
+      <c r="H13" s="30"/>
     </row>
     <row r="14" spans="1:8" ht="118.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7">
+      <c r="A14" s="30">
         <v>11</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="30" t="s">
         <v>190</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="30" t="s">
         <v>188</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="30" t="s">
         <v>189</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="30" t="s">
         <v>191</v>
       </c>
-      <c r="H14" s="7"/>
+      <c r="H14" s="30"/>
     </row>
     <row r="15" spans="1:8" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7">
+      <c r="A15" s="30">
         <v>12</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="30" t="s">
         <v>192</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="30" t="s">
         <v>193</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="30" t="s">
         <v>194</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="30" t="s">
         <v>195</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="30" t="s">
         <v>196</v>
       </c>
-      <c r="H15" s="7"/>
+      <c r="H15" s="30"/>
     </row>
     <row r="16" spans="1:8" ht="174" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="7">
+      <c r="A16" s="30">
         <v>13</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="30" t="s">
         <v>198</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="30" t="s">
         <v>199</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="30" t="s">
         <v>202</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="30" t="s">
         <v>200</v>
       </c>
-      <c r="H16" s="7"/>
+      <c r="H16" s="30"/>
     </row>
     <row r="17" spans="1:8" ht="90.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7">
+      <c r="A17" s="30">
         <v>14</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="30" t="s">
         <v>203</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="30" t="s">
         <v>205</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="30" t="s">
         <v>206</v>
       </c>
-      <c r="H17" s="7"/>
+      <c r="H17" s="30"/>
     </row>
     <row r="18" spans="1:8" ht="88.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7">
+      <c r="A18" s="30">
         <v>15</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="H18" s="7"/>
+      <c r="H18" s="30"/>
     </row>
     <row r="19" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
+      <c r="A19" s="30">
+        <v>16</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>223</v>
+      </c>
+      <c r="G19" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="H19" s="30"/>
     </row>
     <row r="20" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
+      <c r="A20" s="30">
+        <v>17</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="D20" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="E20" s="30" t="s">
+        <v>226</v>
+      </c>
+      <c r="F20" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="G20" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="H20" s="30"/>
     </row>
     <row r="21" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
+      <c r="A21" s="30">
+        <v>18</v>
+      </c>
+      <c r="B21" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="E21" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="G21" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="H21" s="30"/>
     </row>
     <row r="22" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
+      <c r="A22" s="30">
+        <v>19</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>235</v>
+      </c>
+      <c r="E22" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="F22" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="G22" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="H22" s="30"/>
     </row>
     <row r="23" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
+      <c r="A23" s="30">
+        <v>20</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="D23" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="E23" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="F23" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="G23" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="H23" s="30"/>
     </row>
     <row r="24" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
+      <c r="A24" s="30">
+        <v>21</v>
+      </c>
+      <c r="B24" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="E24" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="F24" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="G24" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="H24" s="30"/>
     </row>
     <row r="25" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
+      <c r="A25" s="30">
+        <v>22</v>
+      </c>
+      <c r="B25" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="D25" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="E25" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="F25" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="G25" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="H25" s="30"/>
+    </row>
+    <row r="26" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A26" s="32">
+        <v>23</v>
+      </c>
+      <c r="B26" s="32" t="s">
+        <v>239</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="D26" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="E26" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="F26" s="32" t="s">
+        <v>261</v>
+      </c>
+      <c r="G26" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="H26" s="33"/>
+    </row>
+    <row r="27" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="32">
+        <v>24</v>
+      </c>
+      <c r="B27" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="C27" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="D27" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="E27" s="32" t="s">
+        <v>256</v>
+      </c>
+      <c r="F27" s="32" t="s">
+        <v>262</v>
+      </c>
+      <c r="G27" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="H27" s="33"/>
+    </row>
+    <row r="28" spans="1:8" ht="78" x14ac:dyDescent="0.3">
+      <c r="A28" s="32">
+        <v>25</v>
+      </c>
+      <c r="B28" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="C28" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="D28" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="E28" s="32" t="s">
+        <v>259</v>
+      </c>
+      <c r="F28" s="32" t="s">
+        <v>260</v>
+      </c>
+      <c r="G28" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="H28" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2003,6 +2394,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <tabColor theme="6" tint="0.39997558519241921"/>
+  </sheetPr>
   <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2012,24 +2406,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
     </row>
     <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -2132,28 +2526,64 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
+      <c r="A8" s="7">
+        <v>18</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+      <c r="A9" s="7">
+        <v>21</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
+      <c r="A10" s="7">
+        <v>23</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
@@ -2343,6 +2773,14 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <conditionalFormatting sqref="A4:F10">
+    <cfRule type="expression" priority="2">
+      <formula>AND(ROW()&gt;=4,ROW()&lt;=10)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="1">
+      <formula>AND(ROW()&gt;=4,ROW()&lt;=10)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2359,20 +2797,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -2397,13 +2835,13 @@
       <c r="A6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="20" t="s">
         <v>81</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="20" t="s">
         <v>175</v>
       </c>
     </row>
@@ -2417,7 +2855,7 @@
       <c r="C7" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="20" t="s">
         <v>176</v>
       </c>
     </row>
@@ -2428,10 +2866,10 @@
       <c r="B8" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="20" t="s">
         <v>177</v>
       </c>
     </row>
@@ -2445,7 +2883,7 @@
       <c r="C9" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="20" t="s">
         <v>178</v>
       </c>
     </row>
@@ -2459,7 +2897,7 @@
       <c r="C10" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="20" t="s">
         <v>179</v>
       </c>
     </row>
@@ -2492,7 +2930,7 @@
       <c r="C14" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="D14" s="21" t="s">
+      <c r="D14" s="20" t="s">
         <v>180</v>
       </c>
     </row>
@@ -2506,7 +2944,7 @@
       <c r="C15" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="20" t="s">
         <v>181</v>
       </c>
     </row>
@@ -2520,7 +2958,7 @@
       <c r="C16" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="20" t="s">
         <v>182</v>
       </c>
     </row>
@@ -2534,7 +2972,7 @@
       <c r="C17" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="21" t="s">
         <v>183</v>
       </c>
     </row>
@@ -2548,7 +2986,7 @@
       <c r="C18" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="D18" s="21" t="s">
+      <c r="D18" s="20" t="s">
         <v>184</v>
       </c>
     </row>
